--- a/caja.xlsx
+++ b/caja.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
-  <si>
-    <t>Fecha Actualizacion</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
+  <si>
+    <t>Fecha actualizacion</t>
   </si>
   <si>
     <t>Nominales</t>
@@ -28,51 +28,16 @@
     <t>IOL-MM</t>
   </si>
   <si>
-    <t>$1496032</t>
-  </si>
-  <si>
-    <t>$1497277</t>
-  </si>
-  <si>
-    <t>$1502602,06</t>
-  </si>
-  <si>
-    <t>$2.210.424</t>
-  </si>
-  <si>
-    <t>$2.238.980</t>
-  </si>
-  <si>
-    <t>$2.241.511.17</t>
-  </si>
-  <si>
-    <t>$2.242.638,62</t>
-  </si>
-  <si>
-    <t>$2.247.400</t>
-  </si>
-  <si>
-    <t>$2.000.586</t>
-  </si>
-  <si>
-    <t>$2.795.787</t>
-  </si>
-  <si>
-    <t>$2.799.573</t>
-  </si>
-  <si>
-    <t>$2.802.508</t>
-  </si>
-  <si>
-    <t>$3.832.314</t>
+    <t>2.241.511.17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd.mm.yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="d/MM/yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00)"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -122,7 +87,7 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -363,8 +328,8 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
+      <c r="D2" s="3">
+        <v>1496032.0</v>
       </c>
     </row>
     <row r="3">
@@ -374,8 +339,8 @@
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
+      <c r="D3" s="3">
+        <v>1497277.0</v>
       </c>
     </row>
     <row r="4">
@@ -385,8 +350,8 @@
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
+      <c r="D4" s="3">
+        <v>1502602.06</v>
       </c>
     </row>
     <row r="5">
@@ -396,8 +361,8 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
+      <c r="D5" s="3">
+        <v>2210424.0</v>
       </c>
     </row>
     <row r="6">
@@ -407,8 +372,8 @@
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
+      <c r="D6" s="3">
+        <v>2238980.0</v>
       </c>
     </row>
     <row r="7">
@@ -419,7 +384,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -429,8 +394,8 @@
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
+      <c r="D8" s="3">
+        <v>2242638.62</v>
       </c>
     </row>
     <row r="9">
@@ -440,8 +405,8 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>12</v>
+      <c r="D9" s="3">
+        <v>2247400.0</v>
       </c>
     </row>
     <row r="10">
@@ -451,8 +416,8 @@
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>13</v>
+      <c r="D10" s="3">
+        <v>2000586.0</v>
       </c>
     </row>
     <row r="11">
@@ -462,8 +427,8 @@
       <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
+      <c r="D11" s="3">
+        <v>2795787.0</v>
       </c>
     </row>
     <row r="12">
@@ -473,8 +438,8 @@
       <c r="C12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>15</v>
+      <c r="D12" s="3">
+        <v>2799573.0</v>
       </c>
     </row>
     <row r="13">
@@ -484,8 +449,8 @@
       <c r="C13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>16</v>
+      <c r="D13" s="3">
+        <v>2802508.0</v>
       </c>
     </row>
     <row r="14">
@@ -495,8 +460,8 @@
       <c r="C14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>17</v>
+      <c r="D14" s="3">
+        <v>3832314.0</v>
       </c>
     </row>
   </sheetData>

--- a/caja.xlsx
+++ b/caja.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\dashboard-fi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD434130-0F61-46C8-B524-967A10FF8C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F70D6DD-6982-4ED8-A38C-65AF0473ED0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="iol-mm" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -80,6 +80,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,6 +517,12 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>46183</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3838028.02</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="2"/>
     </row>
@@ -687,6 +694,15 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B16">
+        <v>1000570</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1146052.8799999999</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="2"/>
     </row>
@@ -899,6 +915,15 @@
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B16">
+        <v>64</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1179520</v>
+      </c>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="6:7" x14ac:dyDescent="0.35">

--- a/caja.xlsx
+++ b/caja.xlsx
@@ -1,59 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\dashboard-fi\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F70D6DD-6982-4ED8-A38C-65AF0473ED0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="iol-mm" sheetId="1" r:id="rId1"/>
-    <sheet name="iol-s316" sheetId="2" r:id="rId2"/>
-    <sheet name="iol-spy500" sheetId="3" r:id="rId3"/>
+    <sheet name="iol-mm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="iol-s316" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="iol-spy500" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="gal-mm" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="gal-plus" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="3">
-  <si>
-    <t>Fecha actualizacion</t>
-  </si>
-  <si>
-    <t>nominales</t>
-  </si>
-  <si>
-    <t>saldo</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,30 +52,91 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -360,635 +402,687 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col width="17.26953125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.81640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.26953125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14.1796875" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha actualizacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nominales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2" t="n">
         <v>1496032</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>46148</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="2" t="n">
         <v>1497277</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>46153</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="n">
         <v>1502602.06</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="n">
         <v>2210424</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="2" t="n">
         <v>2238980</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="2" t="n">
         <v>2241511.17</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="2" t="n">
         <v>2242638.62</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="2" t="n">
         <v>2247400</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="2" t="n">
         <v>2000586</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="2" t="n">
         <v>2795787</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="2" t="n">
         <v>2799573</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>46178</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="2" t="n">
         <v>2802508</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>46181</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="2" t="n">
         <v>3832314</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>46182</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="2" t="n">
         <v>3834204</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
         <v>46183</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="2" t="n">
         <v>3838028.02</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F17" s="3"/>
-      <c r="G17" s="2"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{566D581C-CF4D-4949-B149-E31C5C8CD598}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col width="17.26953125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.81640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.26953125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14.1796875" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha actualizacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nominales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2" t="n">
         <v>14911.32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>46148</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="2" t="n">
         <v>14958.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>46153</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="n">
         <v>14999.04</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="n">
         <v>264498</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="2" t="n">
         <v>294737</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="2" t="n">
         <v>294181</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="C8" s="2">
-        <v>294607.34000000003</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+      <c r="C8" s="2" t="n">
+        <v>294607.34</v>
+      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="2" t="n">
         <v>295573</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="2" t="n">
         <v>295408</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="2" t="n">
         <v>644262</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="2" t="n">
         <v>643300</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>46178</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="2" t="n">
         <v>645564</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>46181</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="2" t="n">
         <v>1142600</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>46182</v>
       </c>
-      <c r="C15" s="2">
-        <v>1144341.8999999999</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
+      <c r="C15" s="2" t="n">
+        <v>1144341.9</v>
+      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
         <v>46183</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>1000570</v>
       </c>
-      <c r="C16" s="2">
-        <v>1146052.8799999999</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F17" s="3"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
+      <c r="C16" s="2" t="n">
+        <v>1146052.88</v>
+      </c>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="F20" s="1" t="n"/>
+      <c r="G20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="F21" s="1" t="n"/>
+      <c r="G21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="F22" s="1" t="n"/>
+      <c r="G22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="1" t="n"/>
+      <c r="G23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="F24" s="1" t="n"/>
+      <c r="G24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="F25" s="1" t="n"/>
+      <c r="G25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="F26" s="1" t="n"/>
+      <c r="G26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="F27" s="1" t="n"/>
+      <c r="G27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="F28" s="1" t="n"/>
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="F29" s="1" t="n"/>
+      <c r="G29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="F30" s="1" t="n"/>
+      <c r="G30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="1" t="n"/>
+      <c r="G31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="F32" s="1" t="n"/>
+      <c r="G32" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2391DAAB-1D0F-4789-9AFA-9A287DFEB6A2}">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col width="17.26953125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.81640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.26953125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14.1796875" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha actualizacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nominales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2" t="n">
         <v>484650</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>46148</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="2" t="n">
         <v>485775</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>46153</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="n">
         <v>495450</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="n">
         <v>549000</v>
       </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+      <c r="F5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="2" t="n">
         <v>600875</v>
       </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+      <c r="F6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="2" t="n">
         <v>605275</v>
       </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+      <c r="F7" s="1" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="2" t="n">
         <v>608025</v>
       </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+      <c r="F8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="2" t="n">
         <v>614625</v>
       </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="F9" s="1" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="2" t="n">
         <v>612700</v>
       </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="F10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="2" t="n">
         <v>731250</v>
       </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="F11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="2" t="n">
         <v>744510</v>
       </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="F12" s="1" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>46178</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="2" t="n">
         <v>741390</v>
       </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
+      <c r="F13" s="1" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>46181</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="2" t="n">
         <v>1206400</v>
       </c>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
+      <c r="F14" s="1" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>46182</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="2" t="n">
         <v>1187200</v>
       </c>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
+      <c r="F15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
         <v>46183</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>64</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="2" t="n">
         <v>1179520</v>
       </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F17" s="1"/>
-    </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
+      <c r="F16" s="1" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{b97ea58d-47e6-47cc-9ab7-39ab03def869}" enabled="1" method="Standard" siteId="{505cca53-5750-4134-9501-8d52d5df3cd1}" contentBits="0" removed="0"/>
-</clbl:labelList>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha actualizacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nominales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3213868.83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha actualizacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nominales</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>saldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3546350</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>